--- a/data/trans_camb/P1428-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P1428-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,52</t>
+          <t>-0,72</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-0,14</t>
+          <t>-0,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,1</t>
+          <t>-0,51</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,31</t>
+          <t>-3,13; 2,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 0,69</t>
+          <t>-4,12; 0,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,94; 1,89</t>
+          <t>-3,17; 1,65</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-9,39; -1,51</t>
+          <t>-9,3; -1,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-10,86; -3,14</t>
+          <t>-10,82; -3,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,62</t>
+          <t>-4,26; 2,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,26; -0,19</t>
+          <t>-5,26; -0,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,65; -2,05</t>
+          <t>-6,64; -2,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 2,25</t>
+          <t>-2,74; 1,72</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-8,45%</t>
+          <t>-11,67%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-0,72%</t>
+          <t>-3,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-0,82%</t>
+          <t>-4,05%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 49,45</t>
+          <t>-41,17; 47,06</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-57,87; 16,52</t>
+          <t>-55,58; 12,01</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-38,54; 39,81</t>
+          <t>-42,09; 34,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-44,47; -8,86</t>
+          <t>-44,83; -8,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-51,2; -18,6</t>
+          <t>-51,28; -17,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,77; 21,6</t>
+          <t>-20,59; 17,54</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-38,55; -1,87</t>
+          <t>-38,06; -3,29</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-47,7; -17,71</t>
+          <t>-48,62; -18,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-17,4; 21,08</t>
+          <t>-19,68; 15,17</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-4,04</t>
+          <t>-3,13</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-3,8</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,45</t>
+          <t>-3,44</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 1,1</t>
+          <t>-3,67; 1,03</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,11; -2,06</t>
+          <t>-6,24; -2,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -2,02</t>
+          <t>-5,17; -1,07</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; -1,71</t>
+          <t>-7,88; -1,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-9,53; -3,24</t>
+          <t>-9,86; -3,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-6,9; -0,78</t>
+          <t>-6,97; -0,8</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,11; -1,11</t>
+          <t>-5,03; -1,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,32; -3,38</t>
+          <t>-7,42; -3,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-7,48; -2,44</t>
+          <t>-5,31; -1,65</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-52,88%</t>
+          <t>-40,92%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-21,79%</t>
+          <t>-22,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-35,85%</t>
+          <t>-27,71%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 16,92</t>
+          <t>-40,62; 16,11</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-70,04; -33,1</t>
+          <t>-70,39; -34,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-79,17; -31,31</t>
+          <t>-59,09; -16,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,81; -10,8</t>
+          <t>-41,8; -9,19</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-50,6; -21,07</t>
+          <t>-51,89; -20,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-35,67; -5,07</t>
+          <t>-36,01; -5,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-38,42; -10,2</t>
+          <t>-36,79; -9,07</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-54,72; -30,29</t>
+          <t>-54,29; -30,81</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-59,44; -21,34</t>
+          <t>-39,18; -14,26</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-1,72</t>
+          <t>-1,95</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>12,32</t>
+          <t>-7,03</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,99</t>
+          <t>-4,5</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -0,98</t>
+          <t>-6,0; -1,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,59; -0,77</t>
+          <t>-5,73; -0,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,49; 0,54</t>
+          <t>-4,46; 0,55</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-10,73; -3,1</t>
+          <t>-10,9; -3,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-13,69; -6,94</t>
+          <t>-13,67; -6,62</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 45,86</t>
+          <t>-10,74; -3,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,65; -2,98</t>
+          <t>-7,38; -3,01</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -4,34</t>
+          <t>-8,8; -4,63</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 34,71</t>
+          <t>-6,54; -2,45</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-24,59%</t>
+          <t>-27,89%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,9%</t>
+          <t>-39,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>-36,14%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-70,46; -16,62</t>
+          <t>-69,31; -15,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-64,19; -10,92</t>
+          <t>-64,75; -12,69</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-51,21; 11,64</t>
+          <t>-52,75; 12,76</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-53,45; -19,66</t>
+          <t>-54,51; -21,65</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-69,22; -43,07</t>
+          <t>-68,34; -40,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 291,11</t>
+          <t>-52,48; -22,87</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-55,26; -26,0</t>
+          <t>-54,17; -26,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-63,54; -38,75</t>
+          <t>-64,9; -40,92</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-41,67; 274,83</t>
+          <t>-47,69; -21,27</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-1,47</t>
+          <t>-1,65</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,21</t>
+          <t>-1,72</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,71</t>
+          <t>-1,63</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,41; -0,96</t>
+          <t>-5,23; -0,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,98; -2,91</t>
+          <t>-6,6; -2,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,86</t>
+          <t>-3,62; 0,5</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-7,62; -1,33</t>
+          <t>-7,18; -0,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-12,05; -6,33</t>
+          <t>-12,13; -6,37</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 1,28</t>
+          <t>-4,57; 1,18</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-5,62; -1,6</t>
+          <t>-5,67; -1,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -5,14</t>
+          <t>-9,1; -5,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,84; 0,29</t>
+          <t>-3,6; 0,17</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-19,04%</t>
+          <t>-21,49%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-13,01%</t>
+          <t>-10,11%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-13,59%</t>
+          <t>-12,93%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,14; -12,82</t>
+          <t>-58,6; -11,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-75,78; -40,48</t>
+          <t>-74,44; -40,58</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-41,44; 13,39</t>
+          <t>-41,83; 7,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-40,63; -8,04</t>
+          <t>-38,65; -5,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-65,36; -40,34</t>
+          <t>-65,06; -41,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-32,08; 8,58</t>
+          <t>-24,85; 7,97</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-41,71; -14,43</t>
+          <t>-42,12; -14,8</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-64,64; -44,43</t>
+          <t>-66,47; -45,91</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-28,31; 2,48</t>
+          <t>-26,59; 1,24</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,19</t>
+          <t>-1,97</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,47</t>
+          <t>-3,27</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-0,25</t>
+          <t>-2,58</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; -0,94</t>
+          <t>-3,21; -0,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,63; -2,48</t>
+          <t>-4,76; -2,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,52; -0,98</t>
+          <t>-3,09; -0,86</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,0; -3,59</t>
+          <t>-6,89; -3,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,86; -6,5</t>
+          <t>-10,08; -6,77</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 18,52</t>
+          <t>-4,93; -1,73</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,76; -2,52</t>
+          <t>-4,73; -2,61</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,94; -5,01</t>
+          <t>-6,93; -4,98</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 10,99</t>
+          <t>-3,61; -1,63</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-30,36%</t>
+          <t>-27,25%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>-18,53%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-1,99%</t>
+          <t>-20,59%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-41,41; -13,97</t>
+          <t>-41,1; -12,03</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-59,58; -38,43</t>
+          <t>-60,02; -39,03</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,19; -14,87</t>
+          <t>-39,56; -13,39</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-37,61; -21,33</t>
+          <t>-36,84; -20,64</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-53,52; -39,36</t>
+          <t>-53,63; -39,71</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-21,07; 103,97</t>
+          <t>-26,34; -10,26</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -20,82</t>
+          <t>-36,46; -21,67</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-53,21; -41,94</t>
+          <t>-52,94; -41,1</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,49; 87,72</t>
+          <t>-27,49; -13,63</t>
         </is>
       </c>
     </row>
